--- a/scripts/productos-digitales/guia-churreria/build/checklist-legal-fritura-y-licencias.xlsx
+++ b/scripts/productos-digitales/guia-churreria/build/checklist-legal-fritura-y-licencias.xlsx
@@ -1794,27 +1794,27 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="21">
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2334,14 +2334,14 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A30:E30"/>
   </mergeCells>
   <conditionalFormatting sqref="H7:H14">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3" stopIfTrue="1">
@@ -4740,26 +4740,26 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="20">
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A57:R57"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A58:R58"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C53:P53"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A57:R57"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C53:P53"/>
   </mergeCells>
   <conditionalFormatting sqref="J14:J27">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
@@ -7234,12 +7234,12 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="6">
+    <mergeCell ref="D68:L68"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="A70:M70"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D66:F66"/>
     <mergeCell ref="A71:M71"/>
-    <mergeCell ref="D68:L68"/>
-    <mergeCell ref="A70:M70"/>
-    <mergeCell ref="D66:F66"/>
   </mergeCells>
   <conditionalFormatting sqref="J13">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
@@ -7822,16 +7822,16 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="10">
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B15:B18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
@@ -8234,16 +8234,16 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="10">
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="B13:E13"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A30:E30"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B6 B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Contesta Sí o No" error="Elige «Sí» o «No»." type="list">
@@ -8837,14 +8837,14 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="9">
     <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B16:E16"/>
     <mergeCell ref="B33:E33"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="B18:E18"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B20">
     <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
@@ -9140,12 +9140,12 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="6">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Contesta Sí o No" error="Elige «Sí» o «No»." type="list">
@@ -9635,11 +9635,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="5">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A30:E30"/>
   </mergeCells>
   <conditionalFormatting sqref="B10">
     <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
@@ -10358,22 +10358,22 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="16">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="B34:G34"/>
     <mergeCell ref="A44:G44"/>
-    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B36:G36"/>
     <mergeCell ref="A45:G45"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B31:G31"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="A40:F40"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B29:G29"/>
     <mergeCell ref="B33:G33"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B11:G11"/>
   </mergeCells>
   <conditionalFormatting sqref="B15:F19">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3" stopIfTrue="1">
@@ -11142,9 +11142,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="4">
-    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="C23:K23"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H18">
